--- a/docs/v3.0.0-preview1/StructureDefinition-VRM-maternal-linkage-content-bundle.xlsx
+++ b/docs/v3.0.0-preview1/StructureDefinition-VRM-maternal-linkage-content-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-09T11:35:05-04:00</t>
+    <t>2025-08-11T15:01:09-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1751,17 +1751,17 @@
   <dimension ref="A1:AN156"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="54.52734375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="32.46875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.45703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="20.87109375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="57.953125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="34.23828125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="24.1171875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="22.171875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="97.7421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="100.12109375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1770,26 +1770,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="32.94140625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="34.80859375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="140.34375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.140625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="29.0390625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="146.4296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="44.4375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="31.015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="22.2109375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="86.17578125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="35.9375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="22.43359375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="89.40625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="37.16015625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="29.45703125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/v3.0.0-preview1/StructureDefinition-VRM-maternal-linkage-content-bundle.xlsx
+++ b/docs/v3.0.0-preview1/StructureDefinition-VRM-maternal-linkage-content-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-11T15:01:09-04:00</t>
+    <t>2025-11-25T14:04:25-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -548,7 +548,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -639,7 +639,7 @@
     <t>Bundle.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -8494,7 +8494,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>338</v>
       </c>
@@ -12120,7 +12120,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
         <v>375</v>
       </c>
@@ -15746,7 +15746,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
         <v>415</v>
       </c>
@@ -19490,12 +19490,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN156">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/docs/v3.0.0-preview1/StructureDefinition-VRM-maternal-linkage-content-bundle.xlsx
+++ b/docs/v3.0.0-preview1/StructureDefinition-VRM-maternal-linkage-content-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T14:04:25-05:00</t>
+    <t>2026-03-24T12:23:49-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -548,7 +548,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -639,7 +639,7 @@
     <t>Bundle.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -8494,7 +8494,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>338</v>
       </c>
@@ -12120,7 +12120,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
         <v>375</v>
       </c>
@@ -15746,7 +15746,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
         <v>415</v>
       </c>
@@ -19490,12 +19490,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN156">
-    <filterColumn colId="7">
+    <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="27">
+    <filterColumn colId="26">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
